--- a/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10328"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FA6D4C-C3EC-9F47-ADE3-47FC28318C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2CC703-2333-8A48-8469-48C0AE33BF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3620" yWindow="3260" windowWidth="30160" windowHeight="16880" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3620" yWindow="3260" windowWidth="30160" windowHeight="16880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -146,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="136">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -188,28 +188,6 @@
   </si>
   <si>
     <t>Un cinefil doreşte să îşi dezvolte un program pentru gestionarea filmelor din colecţia personală. Programul va permite următoarele operaţii:</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>F01.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> adăugarea unui film nou (titlu, regizor, an aparitie, actori, categorie, cuvinte cheie);</t>
-    </r>
   </si>
   <si>
     <t>Observații</t>
@@ -728,9 +706,6 @@
     <t>type</t>
   </si>
   <si>
-    <t>TC1_EC</t>
-  </si>
-  <si>
     <t>Pumpkin-Spice latte</t>
   </si>
   <si>
@@ -749,9 +724,6 @@
     <t>Error message - "Pret invalid"</t>
   </si>
   <si>
-    <t>08. price = 2.0</t>
-  </si>
-  <si>
     <t xml:space="preserve">          2.0</t>
   </si>
   <si>
@@ -771,6 +743,21 @@
   </si>
   <si>
     <t>TC6_BVA</t>
+  </si>
+  <si>
+    <t>Steopei Cristian</t>
+  </si>
+  <si>
+    <t>Smarandache Marco</t>
+  </si>
+  <si>
+    <t>Mora Dragos</t>
+  </si>
+  <si>
+    <t>F01. Adaugarea unui produs nou (id, name, price, category, type)</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -1500,7 +1487,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1580,189 +1567,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1771,13 +1575,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1793,34 +1591,22 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="28" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
@@ -1841,7 +1627,211 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2160,12 +2150,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="68"/>
       <c r="H1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2173,11 +2163,11 @@
       <c r="J1" s="32"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H2" s="58" t="s">
+      <c r="H2" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="102"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H3" s="2"/>
@@ -2192,23 +2182,35 @@
       <c r="H4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="J4" s="2">
+        <v>236</v>
+      </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J5" s="2">
+        <v>236</v>
+      </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="18"/>
       <c r="H6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J6" s="2">
+        <v>234</v>
+      </c>
     </row>
     <row r="7" spans="2:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
@@ -2260,8 +2262,8 @@
       <c r="E15" s="1"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
-        <v>14</v>
+      <c r="B16" s="1" t="s">
+        <v>134</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -2274,27 +2276,27 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B18" s="30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C20" s="28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -2311,7 +2313,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -2328,21 +2330,21 @@
     </row>
     <row r="24" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="29"/>
-      <c r="B24" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="57"/>
-      <c r="D24" s="57"/>
-      <c r="E24" s="57"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="57"/>
-      <c r="H24" s="57"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="57"/>
-      <c r="K24" s="57"/>
-      <c r="L24" s="57"/>
-      <c r="M24" s="57"/>
-      <c r="N24" s="57"/>
+      <c r="B24" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="101"/>
+      <c r="D24" s="101"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="101"/>
+      <c r="G24" s="101"/>
+      <c r="H24" s="101"/>
+      <c r="I24" s="101"/>
+      <c r="J24" s="101"/>
+      <c r="K24" s="101"/>
+      <c r="L24" s="101"/>
+      <c r="M24" s="101"/>
+      <c r="N24" s="101"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C26" s="31"/>
@@ -2382,325 +2384,325 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="46"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="68"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B3" s="50" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
+      <c r="B3" s="106" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="108"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="109" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="109"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="109"/>
+      <c r="G5" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="G5" s="54" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
+      <c r="H5" s="110"/>
+      <c r="I5" s="110"/>
+      <c r="J5" s="110"/>
+      <c r="K5" s="110"/>
+      <c r="L5" s="110"/>
+      <c r="M5" s="110"/>
+      <c r="N5" s="110"/>
+      <c r="O5" s="110"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="D6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="G6" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="55" t="s">
+      <c r="H6" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="40" t="s">
+      <c r="I6" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="38" t="s">
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="O6" s="42"/>
+      <c r="O6" s="69"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="47" t="s">
-        <v>69</v>
+      <c r="C7" s="103" t="s">
+        <v>68</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="41"/>
+      <c r="G7" s="111"/>
+      <c r="H7" s="112"/>
       <c r="I7" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="K7" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="L7" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="M7" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="M7" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="N7" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="O7" s="39"/>
+      <c r="N7" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="O7" s="113"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="47"/>
+      <c r="C8" s="103"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="96">
+        <v>70</v>
+      </c>
+      <c r="G8" s="35">
         <v>1</v>
       </c>
-      <c r="H8" s="101" t="s">
+      <c r="H8" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" s="37">
+        <v>1</v>
+      </c>
+      <c r="J8" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="I8" s="98">
-        <v>1</v>
-      </c>
-      <c r="J8" s="97" t="s">
+      <c r="K8" s="37">
+        <v>35</v>
+      </c>
+      <c r="L8" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="K8" s="98">
-        <v>35</v>
-      </c>
-      <c r="L8" s="97" t="s">
+      <c r="M8" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="M8" s="97" t="s">
+      <c r="N8" s="64" t="s">
         <v>100</v>
       </c>
-      <c r="N8" s="99" t="s">
-        <v>101</v>
-      </c>
-      <c r="O8" s="100"/>
+      <c r="O8" s="65"/>
     </row>
     <row r="9" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="47" t="s">
-        <v>74</v>
+      <c r="C9" s="103" t="s">
+        <v>73</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E9" s="4"/>
-      <c r="G9" s="96">
+      <c r="G9" s="35">
         <v>2</v>
       </c>
-      <c r="H9" s="101" t="s">
-        <v>111</v>
-      </c>
-      <c r="I9" s="98">
+      <c r="H9" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="I9" s="37">
         <v>2</v>
       </c>
-      <c r="J9" s="97" t="s">
+      <c r="J9" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="K9" s="37">
+        <v>-50</v>
+      </c>
+      <c r="L9" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="K9" s="98">
-        <v>-50</v>
-      </c>
-      <c r="L9" s="97" t="s">
+      <c r="M9" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="N9" s="64" t="s">
         <v>103</v>
       </c>
-      <c r="M9" s="97" t="s">
-        <v>100</v>
-      </c>
-      <c r="N9" s="99" t="s">
-        <v>104</v>
-      </c>
-      <c r="O9" s="100"/>
+      <c r="O9" s="65"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="47"/>
+      <c r="C10" s="103"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G10" s="96">
+        <v>74</v>
+      </c>
+      <c r="G10" s="35">
         <v>3</v>
       </c>
-      <c r="H10" s="101" t="s">
-        <v>112</v>
-      </c>
-      <c r="I10" s="98">
+      <c r="H10" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="I10" s="37">
         <v>3</v>
       </c>
-      <c r="J10" s="97" t="s">
-        <v>35</v>
-      </c>
-      <c r="K10" s="98">
+      <c r="J10" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="K10" s="37">
         <v>25</v>
       </c>
-      <c r="L10" s="97" t="s">
-        <v>103</v>
-      </c>
-      <c r="M10" s="97" t="s">
-        <v>100</v>
-      </c>
-      <c r="N10" s="99" t="s">
-        <v>105</v>
-      </c>
-      <c r="O10" s="100"/>
+      <c r="L10" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="M10" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="N10" s="64" t="s">
+        <v>104</v>
+      </c>
+      <c r="O10" s="65"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="48" t="s">
-        <v>72</v>
+      <c r="C11" s="104" t="s">
+        <v>71</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E11" s="4"/>
-      <c r="G11" s="96">
+      <c r="G11" s="35">
         <v>4</v>
       </c>
-      <c r="H11" s="101" t="s">
-        <v>113</v>
-      </c>
-      <c r="I11" s="98">
+      <c r="H11" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="I11" s="37">
         <v>-1</v>
       </c>
-      <c r="J11" s="97" t="s">
+      <c r="J11" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="K11" s="37">
+        <v>-25</v>
+      </c>
+      <c r="L11" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="K11" s="98">
-        <v>-25</v>
-      </c>
-      <c r="L11" s="97" t="s">
-        <v>103</v>
-      </c>
-      <c r="M11" s="97" t="s">
-        <v>100</v>
-      </c>
-      <c r="N11" s="99" t="s">
-        <v>106</v>
-      </c>
-      <c r="O11" s="100"/>
+      <c r="M11" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="N11" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="O11" s="65"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="49"/>
+      <c r="C12" s="105"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12" s="96">
+        <v>72</v>
+      </c>
+      <c r="G12" s="35">
         <v>5</v>
       </c>
-      <c r="H12" s="101" t="s">
-        <v>97</v>
-      </c>
-      <c r="I12" s="98">
+      <c r="H12" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="37">
         <v>7</v>
       </c>
-      <c r="J12" s="97" t="s">
+      <c r="J12" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="K12" s="37">
+        <v>30</v>
+      </c>
+      <c r="L12" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="K12" s="98">
-        <v>30</v>
-      </c>
-      <c r="L12" s="97" t="s">
+      <c r="M12" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="M12" s="97" t="s">
-        <v>109</v>
-      </c>
-      <c r="N12" s="99" t="s">
-        <v>101</v>
-      </c>
-      <c r="O12" s="100"/>
+      <c r="N12" s="64" t="s">
+        <v>100</v>
+      </c>
+      <c r="O12" s="65"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="47" t="s">
-        <v>34</v>
+      <c r="C13" s="103" t="s">
+        <v>33</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="G13" s="96">
+      <c r="G13" s="35">
         <v>6</v>
       </c>
-      <c r="H13" s="101" t="s">
-        <v>111</v>
-      </c>
-      <c r="I13" s="98">
+      <c r="H13" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="I13" s="37">
         <v>7</v>
       </c>
-      <c r="J13" s="97" t="s">
+      <c r="J13" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="K13" s="37">
+        <v>-80</v>
+      </c>
+      <c r="L13" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="K13" s="98">
-        <v>-80</v>
-      </c>
-      <c r="L13" s="97" t="s">
+      <c r="M13" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="M13" s="97" t="s">
+      <c r="N13" s="64" t="s">
         <v>109</v>
       </c>
-      <c r="N13" s="99" t="s">
-        <v>110</v>
-      </c>
-      <c r="O13" s="100"/>
+      <c r="O13" s="65"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="47"/>
+      <c r="C14" s="103"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="G14" s="10"/>
@@ -2710,15 +2712,15 @@
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
       <c r="M14" s="9"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="37"/>
+      <c r="N14" s="115"/>
+      <c r="O14" s="116"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="47" t="s">
-        <v>34</v>
+      <c r="C15" s="103" t="s">
+        <v>33</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -2729,14 +2731,14 @@
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="37"/>
+      <c r="N15" s="115"/>
+      <c r="O15" s="116"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="47"/>
+      <c r="C16" s="103"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="G16" s="10"/>
@@ -2746,15 +2748,15 @@
       <c r="K16" s="9"/>
       <c r="L16" s="9"/>
       <c r="M16" s="9"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="37"/>
+      <c r="N16" s="115"/>
+      <c r="O16" s="116"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="47" t="s">
-        <v>34</v>
+      <c r="C17" s="103" t="s">
+        <v>33</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -2765,26 +2767,36 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="37"/>
+      <c r="N17" s="115"/>
+      <c r="O17" s="116"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="47"/>
+      <c r="C18" s="103"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.2">
       <c r="D20" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
+        <v>35</v>
+      </c>
+      <c r="F20" s="114"/>
+      <c r="G20" s="114"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="N13:O13"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="C7:C8"/>
@@ -2801,16 +2813,6 @@
     <mergeCell ref="N11:O11"/>
     <mergeCell ref="N12:O12"/>
     <mergeCell ref="N8:O8"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="I6:M6"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="N13:O13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2842,352 +2844,372 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="46"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="68"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B3" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
+      <c r="B3" s="106" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="108"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="123" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="123"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="3"/>
+      <c r="G5" s="110" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="3"/>
-      <c r="G5" s="54" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="54"/>
+      <c r="H5" s="110"/>
+      <c r="I5" s="110"/>
+      <c r="J5" s="110"/>
+      <c r="K5" s="110"/>
+      <c r="L5" s="110"/>
+      <c r="M5" s="110"/>
+      <c r="N5" s="110"/>
+      <c r="O5" s="110"/>
+      <c r="P5" s="110"/>
+      <c r="Q5" s="110"/>
     </row>
     <row r="6" spans="2:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="G6" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="G6" s="55" t="s">
+      <c r="H6" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="55" t="s">
+      <c r="I6" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="55" t="s">
+      <c r="J6" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="J6" s="40" t="s">
+      <c r="K6" s="124" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="128"/>
+      <c r="M6" s="128"/>
+      <c r="N6" s="128"/>
+      <c r="O6" s="128"/>
+      <c r="P6" s="124" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q6" s="125"/>
+    </row>
+    <row r="7" spans="2:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="104">
+        <v>1</v>
+      </c>
+      <c r="C7" s="118" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G7" s="111"/>
+      <c r="H7" s="111"/>
+      <c r="I7" s="111"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="M7" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="P7" s="70" t="s">
         <v>43</v>
       </c>
-      <c r="K6" s="61" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="62"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="61" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q6" s="63"/>
-    </row>
-    <row r="7" spans="2:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="B7" s="48">
-        <v>1</v>
-      </c>
-      <c r="C7" s="67" t="s">
-        <v>92</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="Q7" s="113"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B8" s="117"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="M7" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="O7" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="P7" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q7" s="39"/>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B8" s="66"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="G8" s="11">
         <v>1</v>
       </c>
-      <c r="H8" s="103">
+      <c r="H8" s="40">
         <v>1</v>
       </c>
-      <c r="I8" s="104" t="s">
-        <v>119</v>
-      </c>
-      <c r="J8" s="105"/>
-      <c r="K8" s="98"/>
-      <c r="L8" s="98"/>
-      <c r="M8" s="98"/>
-      <c r="N8" s="98"/>
-      <c r="O8" s="98"/>
-      <c r="P8" s="99" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q8" s="100"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="K8" s="37">
+        <v>2</v>
+      </c>
+      <c r="L8" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8" s="37">
+        <v>20</v>
+      </c>
+      <c r="N8" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="O8" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="P8" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q8" s="65"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B9" s="66"/>
-      <c r="C9" s="68"/>
+      <c r="B9" s="117"/>
+      <c r="C9" s="119"/>
       <c r="D9" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G9" s="10">
         <v>2</v>
       </c>
-      <c r="H9" s="106">
+      <c r="H9" s="43">
         <v>13</v>
       </c>
-      <c r="I9" s="107"/>
-      <c r="J9" s="107"/>
-      <c r="K9" s="114">
+      <c r="I9" s="44"/>
+      <c r="J9" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="K9" s="47">
         <v>0</v>
       </c>
-      <c r="L9" s="113" t="s">
-        <v>120</v>
-      </c>
-      <c r="M9" s="115">
+      <c r="L9" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="M9" s="48">
         <v>25</v>
       </c>
-      <c r="N9" s="113" t="s">
-        <v>103</v>
-      </c>
-      <c r="O9" s="113" t="s">
-        <v>100</v>
-      </c>
-      <c r="P9" s="108" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q9" s="109"/>
+      <c r="N9" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="O9" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="P9" s="62" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q9" s="63"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B10" s="66"/>
-      <c r="C10" s="68"/>
+      <c r="B10" s="117"/>
+      <c r="C10" s="119"/>
       <c r="D10" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G10" s="11">
         <v>3</v>
       </c>
-      <c r="H10" s="103">
+      <c r="H10" s="40">
         <v>7</v>
       </c>
-      <c r="I10" s="105"/>
-      <c r="J10" s="105"/>
-      <c r="K10" s="110">
+      <c r="I10" s="42"/>
+      <c r="J10" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="K10" s="45">
         <v>1</v>
       </c>
-      <c r="L10" s="97" t="s">
-        <v>120</v>
-      </c>
-      <c r="M10" s="98">
+      <c r="L10" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="M10" s="37">
         <v>0.1</v>
       </c>
-      <c r="N10" s="97" t="s">
-        <v>103</v>
-      </c>
-      <c r="O10" s="97" t="s">
-        <v>100</v>
-      </c>
-      <c r="P10" s="99" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q10" s="100"/>
+      <c r="N10" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="O10" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="P10" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q10" s="65"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B11" s="66"/>
-      <c r="C11" s="68"/>
+      <c r="B11" s="117"/>
+      <c r="C11" s="119"/>
       <c r="D11" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G11" s="11">
         <v>4</v>
       </c>
-      <c r="H11" s="103">
+      <c r="H11" s="40">
         <v>3</v>
       </c>
-      <c r="I11" s="105"/>
-      <c r="J11" s="105"/>
-      <c r="K11" s="110">
+      <c r="I11" s="42"/>
+      <c r="J11" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="K11" s="45">
         <v>1</v>
       </c>
-      <c r="L11" s="97" t="s">
-        <v>122</v>
-      </c>
-      <c r="M11" s="98">
+      <c r="L11" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="M11" s="37">
         <v>25</v>
       </c>
-      <c r="N11" s="97" t="s">
-        <v>103</v>
-      </c>
-      <c r="O11" s="97" t="s">
-        <v>100</v>
-      </c>
-      <c r="P11" s="99" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q11" s="100"/>
+      <c r="N11" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="O11" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="P11" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q11" s="65"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B12" s="49"/>
-      <c r="C12" s="69"/>
+      <c r="B12" s="105"/>
+      <c r="C12" s="120"/>
       <c r="D12" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G12" s="11">
         <v>5</v>
       </c>
-      <c r="H12" s="106">
+      <c r="H12" s="43">
         <v>9</v>
       </c>
-      <c r="I12" s="107"/>
-      <c r="J12" s="107"/>
-      <c r="K12" s="114">
+      <c r="I12" s="44"/>
+      <c r="J12" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="K12" s="47">
         <v>1</v>
       </c>
-      <c r="L12" s="113" t="s">
-        <v>120</v>
-      </c>
-      <c r="M12" s="115">
+      <c r="L12" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="M12" s="48">
         <v>0</v>
       </c>
-      <c r="N12" s="113" t="s">
-        <v>103</v>
-      </c>
-      <c r="O12" s="113" t="s">
-        <v>100</v>
-      </c>
-      <c r="P12" s="111" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q12" s="112"/>
+      <c r="N12" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="O12" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="P12" s="77" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q12" s="78"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B13" s="48">
+      <c r="B13" s="104">
         <v>2</v>
       </c>
-      <c r="C13" s="48" t="s">
-        <v>77</v>
+      <c r="C13" s="104" t="s">
+        <v>76</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G13" s="10">
         <v>6</v>
       </c>
-      <c r="H13" s="106">
+      <c r="H13" s="43">
         <v>8</v>
       </c>
-      <c r="I13" s="107"/>
-      <c r="J13" s="107"/>
-      <c r="K13" s="114">
+      <c r="I13" s="44"/>
+      <c r="J13" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="K13" s="47">
         <v>7</v>
       </c>
-      <c r="L13" s="113" t="s">
-        <v>107</v>
-      </c>
-      <c r="M13" s="113" t="s">
-        <v>127</v>
-      </c>
-      <c r="N13" s="113" t="s">
+      <c r="L13" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="M13" s="46" t="s">
         <v>124</v>
       </c>
-      <c r="O13" s="113" t="s">
-        <v>109</v>
-      </c>
-      <c r="P13" s="108" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q13" s="109"/>
+      <c r="N13" s="46" t="s">
+        <v>122</v>
+      </c>
+      <c r="O13" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="P13" s="62" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q13" s="63"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="2" t="s">
-        <v>126</v>
-      </c>
+      <c r="B14" s="117"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="2"/>
       <c r="G14" s="11">
         <v>7</v>
       </c>
-      <c r="H14" s="103">
+      <c r="H14" s="40">
         <v>9</v>
       </c>
-      <c r="I14" s="105"/>
-      <c r="J14" s="105"/>
-      <c r="K14" s="110">
+      <c r="I14" s="42"/>
+      <c r="J14" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="K14" s="45">
         <v>7</v>
       </c>
-      <c r="L14" s="97" t="s">
-        <v>107</v>
-      </c>
-      <c r="M14" s="98">
+      <c r="L14" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="M14" s="37">
         <v>0</v>
       </c>
-      <c r="N14" s="97" t="s">
-        <v>124</v>
-      </c>
-      <c r="O14" s="97" t="s">
-        <v>109</v>
-      </c>
-      <c r="P14" s="99" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q14" s="100"/>
+      <c r="N14" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="O14" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="P14" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q14" s="65"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
+      <c r="B15" s="117"/>
+      <c r="C15" s="117"/>
       <c r="D15" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G15" s="11">
         <v>8</v>
@@ -3200,14 +3222,14 @@
       <c r="M15" s="16"/>
       <c r="N15" s="16"/>
       <c r="O15" s="16"/>
-      <c r="P15" s="59"/>
-      <c r="Q15" s="60"/>
+      <c r="P15" s="126"/>
+      <c r="Q15" s="127"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
+      <c r="B16" s="117"/>
+      <c r="C16" s="117"/>
       <c r="D16" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G16" s="11">
         <v>9</v>
@@ -3220,14 +3242,14 @@
       <c r="M16" s="16"/>
       <c r="N16" s="16"/>
       <c r="O16" s="16"/>
-      <c r="P16" s="59"/>
-      <c r="Q16" s="60"/>
+      <c r="P16" s="126"/>
+      <c r="Q16" s="127"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B17" s="66"/>
-      <c r="C17" s="66"/>
+      <c r="B17" s="117"/>
+      <c r="C17" s="117"/>
       <c r="D17" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G17" s="11">
         <v>10</v>
@@ -3240,14 +3262,14 @@
       <c r="M17" s="16"/>
       <c r="N17" s="16"/>
       <c r="O17" s="16"/>
-      <c r="P17" s="59"/>
-      <c r="Q17" s="60"/>
+      <c r="P17" s="126"/>
+      <c r="Q17" s="127"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
+      <c r="B18" s="105"/>
+      <c r="C18" s="105"/>
       <c r="D18" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G18" s="11">
         <v>11</v>
@@ -3260,18 +3282,18 @@
       <c r="M18" s="16"/>
       <c r="N18" s="16"/>
       <c r="O18" s="16"/>
-      <c r="P18" s="59"/>
-      <c r="Q18" s="60"/>
+      <c r="P18" s="126"/>
+      <c r="Q18" s="127"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B19" s="48">
+      <c r="B19" s="104">
         <v>3</v>
       </c>
-      <c r="C19" s="67" t="s">
+      <c r="C19" s="118" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="G19" s="11">
         <v>12</v>
@@ -3284,14 +3306,14 @@
       <c r="M19" s="16"/>
       <c r="N19" s="16"/>
       <c r="O19" s="16"/>
-      <c r="P19" s="59"/>
-      <c r="Q19" s="60"/>
+      <c r="P19" s="126"/>
+      <c r="Q19" s="127"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B20" s="66"/>
-      <c r="C20" s="68"/>
+      <c r="B20" s="117"/>
+      <c r="C20" s="119"/>
       <c r="D20" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G20" s="11">
         <v>13</v>
@@ -3304,14 +3326,14 @@
       <c r="M20" s="16"/>
       <c r="N20" s="16"/>
       <c r="O20" s="16"/>
-      <c r="P20" s="59"/>
-      <c r="Q20" s="60"/>
+      <c r="P20" s="126"/>
+      <c r="Q20" s="127"/>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B21" s="66"/>
-      <c r="C21" s="68"/>
+      <c r="B21" s="117"/>
+      <c r="C21" s="119"/>
       <c r="D21" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G21" s="11">
         <v>14</v>
@@ -3324,14 +3346,14 @@
       <c r="M21" s="16"/>
       <c r="N21" s="16"/>
       <c r="O21" s="16"/>
-      <c r="P21" s="59"/>
-      <c r="Q21" s="60"/>
+      <c r="P21" s="126"/>
+      <c r="Q21" s="127"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B22" s="66"/>
-      <c r="C22" s="68"/>
+      <c r="B22" s="117"/>
+      <c r="C22" s="119"/>
       <c r="D22" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G22" s="11">
         <v>15</v>
@@ -3344,14 +3366,14 @@
       <c r="M22" s="16"/>
       <c r="N22" s="16"/>
       <c r="O22" s="16"/>
-      <c r="P22" s="59"/>
-      <c r="Q22" s="60"/>
+      <c r="P22" s="126"/>
+      <c r="Q22" s="127"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B23" s="66"/>
-      <c r="C23" s="68"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="119"/>
       <c r="D23" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G23" s="11">
         <v>16</v>
@@ -3364,14 +3386,14 @@
       <c r="M23" s="16"/>
       <c r="N23" s="16"/>
       <c r="O23" s="16"/>
-      <c r="P23" s="59"/>
-      <c r="Q23" s="60"/>
+      <c r="P23" s="126"/>
+      <c r="Q23" s="127"/>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B24" s="49"/>
-      <c r="C24" s="69"/>
+      <c r="B24" s="105"/>
+      <c r="C24" s="120"/>
       <c r="D24" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G24" s="11">
         <v>17</v>
@@ -3384,16 +3406,16 @@
       <c r="M24" s="16"/>
       <c r="N24" s="16"/>
       <c r="O24" s="16"/>
-      <c r="P24" s="59"/>
-      <c r="Q24" s="60"/>
+      <c r="P24" s="126"/>
+      <c r="Q24" s="127"/>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B25" s="48">
+      <c r="B25" s="104">
         <v>4</v>
       </c>
-      <c r="C25" s="67"/>
+      <c r="C25" s="118"/>
       <c r="D25" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G25" s="11">
         <v>18</v>
@@ -3406,60 +3428,84 @@
       <c r="M25" s="16"/>
       <c r="N25" s="16"/>
       <c r="O25" s="16"/>
-      <c r="P25" s="59"/>
-      <c r="Q25" s="60"/>
+      <c r="P25" s="126"/>
+      <c r="Q25" s="127"/>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B26" s="66"/>
-      <c r="C26" s="68"/>
+      <c r="B26" s="117"/>
+      <c r="C26" s="119"/>
       <c r="D26" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B27" s="66"/>
-      <c r="C27" s="68"/>
+      <c r="B27" s="117"/>
+      <c r="C27" s="119"/>
       <c r="D27" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B28" s="66"/>
-      <c r="C28" s="68"/>
+      <c r="B28" s="117"/>
+      <c r="C28" s="119"/>
       <c r="D28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="64"/>
-      <c r="J28" s="64"/>
-      <c r="K28" s="64"/>
-      <c r="L28" s="64"/>
-      <c r="M28" s="64"/>
+        <v>33</v>
+      </c>
+      <c r="G28" s="114"/>
+      <c r="H28" s="114"/>
+      <c r="I28" s="122"/>
+      <c r="J28" s="122"/>
+      <c r="K28" s="122"/>
+      <c r="L28" s="122"/>
+      <c r="M28" s="122"/>
       <c r="N28" s="24"/>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B29" s="66"/>
-      <c r="C29" s="68"/>
+      <c r="B29" s="117"/>
+      <c r="C29" s="119"/>
       <c r="D29" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I29" s="70"/>
-      <c r="J29" s="70"/>
-      <c r="K29" s="70"/>
-      <c r="L29" s="70"/>
-      <c r="M29" s="70"/>
+        <v>33</v>
+      </c>
+      <c r="I29" s="121"/>
+      <c r="J29" s="121"/>
+      <c r="K29" s="121"/>
+      <c r="L29" s="121"/>
+      <c r="M29" s="121"/>
       <c r="N29" s="25"/>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B30" s="49"/>
-      <c r="C30" s="69"/>
+      <c r="B30" s="105"/>
+      <c r="C30" s="120"/>
       <c r="D30" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="K6:O6"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:M28"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="I6:I7"/>
@@ -3476,30 +3522,6 @@
     <mergeCell ref="G5:Q5"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="I28:M28"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="K6:O6"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="P12:Q12"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3521,83 +3543,83 @@
     <col min="8" max="8" width="10.5" customWidth="1"/>
     <col min="9" max="9" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="27" customWidth="1"/>
-    <col min="11" max="11" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="48" customWidth="1"/>
+    <col min="12" max="12" width="37.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="46"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="68"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B3" s="95" t="s">
+      <c r="B3" s="76" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="76"/>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B4" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="95"/>
-      <c r="I3" s="95"/>
-      <c r="J3" s="95"/>
-      <c r="K3" s="95"/>
-      <c r="L3" s="95"/>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B4" s="55" t="s">
+      <c r="C4" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="93" t="s">
+      <c r="D4" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="81" t="s">
+      <c r="E4" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="F4" s="70" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="69" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="69"/>
+    </row>
+    <row r="5" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="81"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="13" t="s">
         <v>49</v>
-      </c>
-      <c r="F4" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="42"/>
-    </row>
-    <row r="5" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="80"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="92"/>
-      <c r="F5" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" s="13" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="16" thickTop="1" x14ac:dyDescent="0.2">
@@ -3605,31 +3627,33 @@
         <v>1</v>
       </c>
       <c r="C6" s="79" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="14" t="s">
-        <v>52</v>
-      </c>
       <c r="E6" s="12"/>
-      <c r="F6" s="98">
+      <c r="F6" s="37">
         <v>1</v>
       </c>
-      <c r="G6" s="97" t="s">
+      <c r="G6" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="H6" s="37">
+        <v>35</v>
+      </c>
+      <c r="I6" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="H6" s="98">
-        <v>35</v>
-      </c>
-      <c r="I6" s="97" t="s">
+      <c r="J6" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="J6" s="97" t="s">
+      <c r="K6" s="130" t="s">
         <v>100</v>
       </c>
-      <c r="K6" s="99" t="s">
-        <v>101</v>
-      </c>
-      <c r="L6" s="100"/>
+      <c r="L6" s="130" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B7" s="6">
@@ -3638,28 +3662,30 @@
       </c>
       <c r="C7" s="79"/>
       <c r="D7" s="15" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E7" s="6"/>
-      <c r="F7" s="98">
+      <c r="F7" s="37">
         <v>2</v>
       </c>
-      <c r="G7" s="97" t="s">
+      <c r="G7" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="H7" s="37">
+        <v>-50</v>
+      </c>
+      <c r="I7" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="H7" s="98">
-        <v>-50</v>
-      </c>
-      <c r="I7" s="97" t="s">
+      <c r="J7" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="K7" s="130" t="s">
         <v>103</v>
       </c>
-      <c r="J7" s="97" t="s">
-        <v>100</v>
-      </c>
-      <c r="K7" s="99" t="s">
-        <v>104</v>
-      </c>
-      <c r="L7" s="100"/>
+      <c r="L7" s="130" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B8" s="6">
@@ -3668,28 +3694,30 @@
       </c>
       <c r="C8" s="79"/>
       <c r="D8" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E8" s="6"/>
-      <c r="F8" s="98">
+      <c r="F8" s="37">
         <v>3</v>
       </c>
-      <c r="G8" s="97" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="98">
+      <c r="G8" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="37">
         <v>25</v>
       </c>
-      <c r="I8" s="97" t="s">
-        <v>103</v>
-      </c>
-      <c r="J8" s="97" t="s">
-        <v>100</v>
-      </c>
-      <c r="K8" s="99" t="s">
-        <v>105</v>
-      </c>
-      <c r="L8" s="100"/>
+      <c r="I8" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="J8" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="K8" s="130" t="s">
+        <v>104</v>
+      </c>
+      <c r="L8" s="130" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B9" s="6">
@@ -3698,28 +3726,30 @@
       </c>
       <c r="C9" s="79"/>
       <c r="D9" s="15" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E9" s="6"/>
-      <c r="F9" s="98">
+      <c r="F9" s="37">
         <v>-1</v>
       </c>
-      <c r="G9" s="97" t="s">
+      <c r="G9" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9" s="37">
+        <v>-25</v>
+      </c>
+      <c r="I9" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="H9" s="98">
-        <v>-25</v>
-      </c>
-      <c r="I9" s="97" t="s">
-        <v>103</v>
-      </c>
-      <c r="J9" s="97" t="s">
-        <v>100</v>
-      </c>
-      <c r="K9" s="99" t="s">
-        <v>106</v>
-      </c>
-      <c r="L9" s="100"/>
+      <c r="J9" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="K9" s="130" t="s">
+        <v>105</v>
+      </c>
+      <c r="L9" s="130" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B10" s="6">
@@ -3728,28 +3758,30 @@
       </c>
       <c r="C10" s="79"/>
       <c r="D10" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" s="6"/>
-      <c r="F10" s="98">
+      <c r="F10" s="37">
         <v>7</v>
       </c>
-      <c r="G10" s="97" t="s">
+      <c r="G10" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="H10" s="37">
+        <v>30</v>
+      </c>
+      <c r="I10" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="H10" s="98">
-        <v>30</v>
-      </c>
-      <c r="I10" s="97" t="s">
+      <c r="J10" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="J10" s="97" t="s">
-        <v>109</v>
-      </c>
-      <c r="K10" s="99" t="s">
-        <v>101</v>
-      </c>
-      <c r="L10" s="100"/>
+      <c r="K10" s="130" t="s">
+        <v>100</v>
+      </c>
+      <c r="L10" s="130" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B11" s="6">
@@ -3758,28 +3790,30 @@
       </c>
       <c r="C11" s="79"/>
       <c r="D11" s="15" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E11" s="6"/>
-      <c r="F11" s="98">
+      <c r="F11" s="37">
         <v>7</v>
       </c>
-      <c r="G11" s="97" t="s">
+      <c r="G11" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="H11" s="37">
+        <v>-80</v>
+      </c>
+      <c r="I11" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="H11" s="98">
-        <v>-80</v>
-      </c>
-      <c r="I11" s="97" t="s">
+      <c r="J11" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="J11" s="97" t="s">
+      <c r="K11" s="130" t="s">
         <v>109</v>
       </c>
-      <c r="K11" s="99" t="s">
-        <v>110</v>
-      </c>
-      <c r="L11" s="100"/>
+      <c r="L11" s="130" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B12" s="6">
@@ -3789,272 +3823,285 @@
       <c r="C12" s="79"/>
       <c r="D12" s="15"/>
       <c r="E12" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="F12" s="114">
+        <v>128</v>
+      </c>
+      <c r="F12" s="47">
         <v>0</v>
       </c>
-      <c r="G12" s="113" t="s">
-        <v>120</v>
-      </c>
-      <c r="H12" s="115">
+      <c r="G12" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="H12" s="48">
         <v>25</v>
       </c>
-      <c r="I12" s="113" t="s">
-        <v>103</v>
-      </c>
-      <c r="J12" s="113" t="s">
-        <v>100</v>
-      </c>
-      <c r="K12" s="108" t="s">
-        <v>121</v>
-      </c>
-      <c r="L12" s="109"/>
+      <c r="I12" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="J12" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="K12" s="129" t="s">
+        <v>119</v>
+      </c>
+      <c r="L12" s="129" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B13" s="123">
+      <c r="B13" s="56">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C13" s="79"/>
       <c r="D13" s="34"/>
-      <c r="E13" s="123" t="s">
-        <v>132</v>
-      </c>
-      <c r="F13" s="110">
+      <c r="E13" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="F13" s="45">
         <v>1</v>
       </c>
-      <c r="G13" s="97" t="s">
-        <v>120</v>
-      </c>
-      <c r="H13" s="98">
+      <c r="G13" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="H13" s="37">
         <v>0.1</v>
       </c>
-      <c r="I13" s="97" t="s">
-        <v>103</v>
-      </c>
-      <c r="J13" s="97" t="s">
-        <v>100</v>
-      </c>
-      <c r="K13" s="99" t="s">
-        <v>33</v>
-      </c>
-      <c r="L13" s="100"/>
+      <c r="I13" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="J13" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="K13" s="130" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" s="130" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B14" s="33"/>
-      <c r="C14" s="125"/>
+      <c r="C14" s="58"/>
       <c r="D14" s="15"/>
       <c r="E14" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F14" s="121">
+        <v>54</v>
+      </c>
+      <c r="F14" s="54">
         <v>1</v>
       </c>
-      <c r="G14" s="97" t="s">
-        <v>122</v>
-      </c>
-      <c r="H14" s="98">
+      <c r="G14" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="H14" s="37">
         <v>25</v>
       </c>
-      <c r="I14" s="97" t="s">
-        <v>103</v>
-      </c>
-      <c r="J14" s="97" t="s">
-        <v>100</v>
-      </c>
-      <c r="K14" s="99" t="s">
-        <v>33</v>
-      </c>
-      <c r="L14" s="100"/>
+      <c r="I14" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="J14" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="K14" s="130" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14" s="130" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="15" spans="2:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="6"/>
-      <c r="C15" s="127"/>
+      <c r="C15" s="60"/>
       <c r="D15" s="11"/>
       <c r="E15" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" s="122">
+        <v>55</v>
+      </c>
+      <c r="F15" s="55">
         <v>1</v>
       </c>
-      <c r="G15" s="113" t="s">
-        <v>120</v>
-      </c>
-      <c r="H15" s="115">
+      <c r="G15" s="46" t="s">
+        <v>118</v>
+      </c>
+      <c r="H15" s="48">
         <v>0</v>
       </c>
-      <c r="I15" s="113" t="s">
-        <v>103</v>
-      </c>
-      <c r="J15" s="113" t="s">
-        <v>100</v>
-      </c>
-      <c r="K15" s="111" t="s">
-        <v>123</v>
-      </c>
-      <c r="L15" s="112"/>
+      <c r="I15" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="J15" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="K15" s="131" t="s">
+        <v>121</v>
+      </c>
+      <c r="L15" s="131" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B16" s="2"/>
-      <c r="C16" s="128"/>
-      <c r="D16" s="126"/>
-      <c r="E16" s="124" t="s">
-        <v>57</v>
-      </c>
-      <c r="F16" s="122">
+      <c r="C16" s="61"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="55">
         <v>7</v>
       </c>
-      <c r="G16" s="113" t="s">
-        <v>107</v>
-      </c>
-      <c r="H16" s="113" t="s">
-        <v>127</v>
-      </c>
-      <c r="I16" s="113" t="s">
+      <c r="G16" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="H16" s="46" t="s">
         <v>124</v>
       </c>
-      <c r="J16" s="113" t="s">
-        <v>109</v>
-      </c>
-      <c r="K16" s="108" t="s">
-        <v>33</v>
-      </c>
-      <c r="L16" s="109"/>
+      <c r="I16" s="46" t="s">
+        <v>122</v>
+      </c>
+      <c r="J16" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="K16" s="129" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16" s="129" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B17" s="2"/>
-      <c r="C17" s="128"/>
-      <c r="D17" s="126"/>
-      <c r="E17" s="124" t="s">
-        <v>133</v>
-      </c>
-      <c r="F17" s="121">
+      <c r="C17" s="61"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="F17" s="54">
         <v>7</v>
       </c>
-      <c r="G17" s="97" t="s">
-        <v>107</v>
-      </c>
-      <c r="H17" s="98">
+      <c r="G17" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" s="37">
         <v>0</v>
       </c>
-      <c r="I17" s="97" t="s">
-        <v>124</v>
-      </c>
-      <c r="J17" s="97" t="s">
-        <v>109</v>
-      </c>
-      <c r="K17" s="102" t="s">
-        <v>125</v>
+      <c r="I17" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="J17" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="K17" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="L17" s="38" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F18" s="116"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="119"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="50"/>
+      <c r="K18" s="51"/>
+      <c r="L18" s="52"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="D19" s="120"/>
-      <c r="F19" s="116"/>
-      <c r="G19" s="117"/>
-      <c r="H19" s="117"/>
-      <c r="I19" s="117"/>
-      <c r="J19" s="117"/>
-      <c r="K19" s="118"/>
-      <c r="L19" s="119"/>
+      <c r="D19" s="53"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="51"/>
+      <c r="L19" s="52"/>
     </row>
     <row r="20" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="F20" s="116"/>
-      <c r="G20" s="117"/>
-      <c r="H20" s="117"/>
-      <c r="I20" s="117"/>
-      <c r="J20" s="117"/>
-      <c r="K20" s="118"/>
-      <c r="L20" s="119"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="51"/>
+      <c r="L20" s="52"/>
     </row>
     <row r="21" spans="2:14" ht="16" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="C21" s="73" t="s">
+      <c r="C21" s="90" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="91"/>
+      <c r="E21" s="91"/>
+      <c r="F21" s="92"/>
+      <c r="G21" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="D21" s="75"/>
-      <c r="E21" s="75"/>
-      <c r="F21" s="76"/>
-      <c r="G21" s="20" t="s">
+      <c r="H21" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="H21" s="73" t="s">
+      <c r="I21" s="93"/>
+      <c r="J21" s="91"/>
+      <c r="K21" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="I21" s="74"/>
-      <c r="J21" s="75"/>
-      <c r="K21" s="73" t="s">
+      <c r="L21" s="93"/>
+      <c r="M21" s="91"/>
+      <c r="N21" s="92"/>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B22" s="86" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="L21" s="74"/>
-      <c r="M21" s="75"/>
-      <c r="N21" s="76"/>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B22" s="85" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="86" t="s">
+      <c r="D22" s="88" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="72" t="s">
+      <c r="E22" s="88" t="s">
         <v>63</v>
       </c>
-      <c r="E22" s="72" t="s">
+      <c r="F22" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="F22" s="71" t="s">
+      <c r="G22" s="98" t="s">
         <v>65</v>
       </c>
-      <c r="G22" s="91" t="s">
+      <c r="H22" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="H22" s="87" t="s">
-        <v>67</v>
-      </c>
-      <c r="I22" s="88"/>
-      <c r="J22" s="72" t="s">
+      <c r="I22" s="95"/>
+      <c r="J22" s="88" t="s">
+        <v>61</v>
+      </c>
+      <c r="K22" s="99" t="s">
+        <v>66</v>
+      </c>
+      <c r="L22" s="88" t="s">
+        <v>61</v>
+      </c>
+      <c r="M22" s="88" t="s">
         <v>62</v>
       </c>
-      <c r="K22" s="77" t="s">
-        <v>67</v>
-      </c>
-      <c r="L22" s="72" t="s">
-        <v>62</v>
-      </c>
-      <c r="M22" s="72" t="s">
+      <c r="N22" s="89" t="s">
         <v>63</v>
       </c>
-      <c r="N22" s="71" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B23" s="85"/>
-      <c r="C23" s="86"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="91"/>
-      <c r="H23" s="89"/>
-      <c r="I23" s="90"/>
-      <c r="J23" s="72"/>
-      <c r="K23" s="78"/>
-      <c r="L23" s="72"/>
-      <c r="M23" s="72"/>
-      <c r="N23" s="71"/>
+      <c r="B23" s="86"/>
+      <c r="C23" s="87"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="88"/>
+      <c r="F23" s="89"/>
+      <c r="G23" s="98"/>
+      <c r="H23" s="96"/>
+      <c r="I23" s="97"/>
+      <c r="J23" s="88"/>
+      <c r="K23" s="100"/>
+      <c r="L23" s="88"/>
+      <c r="M23" s="88"/>
+      <c r="N23" s="89"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B24" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C24" s="19">
         <v>12</v>
@@ -4067,15 +4114,15 @@
       </c>
       <c r="F24" s="22"/>
       <c r="G24" s="27"/>
-      <c r="H24" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="I24" s="84"/>
+      <c r="H24" s="84" t="s">
+        <v>67</v>
+      </c>
+      <c r="I24" s="85"/>
       <c r="J24" s="2">
         <v>3</v>
       </c>
       <c r="K24" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L24" s="2">
         <v>12</v>
@@ -4091,24 +4138,17 @@
       <c r="K25" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="F4:J4"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="K15:L15"/>
+  <mergeCells count="25">
+    <mergeCell ref="M22:M23"/>
+    <mergeCell ref="N22:N23"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="G22:G23"/>
     <mergeCell ref="C6:C13"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="D4:D5"/>
@@ -4118,16 +4158,12 @@
     <mergeCell ref="D22:D23"/>
     <mergeCell ref="E22:E23"/>
     <mergeCell ref="F22:F23"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:I23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="M22:M23"/>
-    <mergeCell ref="N22:N23"/>
-    <mergeCell ref="K21:N21"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B3:L3"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4275,18 +4311,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4308,18 +4344,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>